--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149872</v>
       </c>
       <c r="B2" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121149873</v>
       </c>
       <c r="B3" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149874</v>
+        <v>121149871</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +913,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489640</v>
+        <v>490125</v>
       </c>
       <c r="R4" t="n">
-        <v>6839220</v>
+        <v>6838707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149871</v>
+        <v>121149874</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490125</v>
+        <v>489640</v>
       </c>
       <c r="R5" t="n">
-        <v>6838707</v>
+        <v>6839220</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149872</v>
+        <v>121149871</v>
       </c>
       <c r="B2" t="n">
-        <v>79683</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490021</v>
+        <v>490125</v>
       </c>
       <c r="R2" t="n">
-        <v>6838896</v>
+        <v>6838707</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149873</v>
+        <v>121149874</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489795</v>
+        <v>489640</v>
       </c>
       <c r="R3" t="n">
-        <v>6839465</v>
+        <v>6839220</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149871</v>
+        <v>121149873</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490125</v>
+        <v>489795</v>
       </c>
       <c r="R4" t="n">
-        <v>6838707</v>
+        <v>6839465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149874</v>
+        <v>121149872</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>79683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489640</v>
+        <v>490021</v>
       </c>
       <c r="R5" t="n">
-        <v>6839220</v>
+        <v>6838896</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149871</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149874</v>
+        <v>121149872</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>79686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489640</v>
+        <v>490021</v>
       </c>
       <c r="R3" t="n">
-        <v>6839220</v>
+        <v>6838896</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149873</v>
+        <v>121149874</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489795</v>
+        <v>489640</v>
       </c>
       <c r="R4" t="n">
-        <v>6839465</v>
+        <v>6839220</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149872</v>
+        <v>121149873</v>
       </c>
       <c r="B5" t="n">
-        <v>79683</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490021</v>
+        <v>489795</v>
       </c>
       <c r="R5" t="n">
-        <v>6838896</v>
+        <v>6839465</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149871</v>
+        <v>121149872</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>79686</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490125</v>
+        <v>490021</v>
       </c>
       <c r="R2" t="n">
-        <v>6838707</v>
+        <v>6838896</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149872</v>
+        <v>121149874</v>
       </c>
       <c r="B3" t="n">
-        <v>79686</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490021</v>
+        <v>489640</v>
       </c>
       <c r="R3" t="n">
-        <v>6838896</v>
+        <v>6839220</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149874</v>
+        <v>121149873</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489640</v>
+        <v>489795</v>
       </c>
       <c r="R4" t="n">
-        <v>6839220</v>
+        <v>6839465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149873</v>
+        <v>121149871</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489795</v>
+        <v>490125</v>
       </c>
       <c r="R5" t="n">
-        <v>6839465</v>
+        <v>6838707</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149872</v>
       </c>
       <c r="B2" t="n">
-        <v>79686</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149874</v>
+        <v>121149873</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>78343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489640</v>
+        <v>489795</v>
       </c>
       <c r="R3" t="n">
-        <v>6839220</v>
+        <v>6839465</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149873</v>
+        <v>121149871</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489795</v>
+        <v>490125</v>
       </c>
       <c r="R4" t="n">
-        <v>6839465</v>
+        <v>6838707</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149871</v>
+        <v>121149874</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490125</v>
+        <v>489640</v>
       </c>
       <c r="R5" t="n">
-        <v>6838707</v>
+        <v>6839220</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149872</v>
+        <v>121149874</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490021</v>
+        <v>489640</v>
       </c>
       <c r="R2" t="n">
-        <v>6838896</v>
+        <v>6839220</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149873</v>
+        <v>121149872</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,14 +826,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489795</v>
+        <v>490021</v>
       </c>
       <c r="R3" t="n">
-        <v>6839465</v>
+        <v>6838896</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149871</v>
+        <v>121149873</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490125</v>
+        <v>489795</v>
       </c>
       <c r="R4" t="n">
-        <v>6838707</v>
+        <v>6839465</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149874</v>
+        <v>121149871</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489640</v>
+        <v>490125</v>
       </c>
       <c r="R5" t="n">
-        <v>6839220</v>
+        <v>6838707</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 48689-2024 artfynd.xlsx
+++ b/artfynd/A 48689-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149874</v>
+        <v>121149872</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tandsjöborg, Dlr</t>
+          <t>Lillhamra, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489640</v>
+        <v>490021</v>
       </c>
       <c r="R2" t="n">
-        <v>6839220</v>
+        <v>6838896</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149872</v>
+        <v>121149874</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillhamra, Dlr</t>
+          <t>Tandsjöborg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490021</v>
+        <v>489640</v>
       </c>
       <c r="R3" t="n">
-        <v>6838896</v>
+        <v>6839220</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
